--- a/reports/二级子公司C_利润表_2025-03.xlsx
+++ b/reports/二级子公司C_利润表_2025-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>88531608</v>
+        <v>89886580</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>85995573</v>
+        <v>85314001</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>236417156</v>
+        <v>236428944</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>398516</v>
+        <v>400799</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1104701</v>
+        <v>1101710</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>348139</v>
+        <v>351450</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>964745</v>
+        <v>965811</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>298203</v>
+        <v>301668</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>825511</v>
+        <v>829421</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>278430</v>
+        <v>281679</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>769568</v>
+        <v>775371</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>149364</v>
+        <v>150807</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>412085</v>
+        <v>415801</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>119745</v>
+        <v>120458</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>329792</v>
+        <v>332727</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>86939211</v>
+        <v>88279719</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>84403176</v>
+        <v>83707140</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>80377834</v>
+        <v>79737382</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>220903603</v>
+        <v>221028415</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1206990</v>
+        <v>1193935</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3319666</v>
+        <v>3309002</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>804722</v>
+        <v>795251</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2216287</v>
+        <v>2202069</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3014823</v>
+        <v>2982681</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>8317517</v>
+        <v>8246935</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>401244</v>
+        <v>398162</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1108980</v>
+        <v>1098923</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>300220</v>
+        <v>299218</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>831063</v>
+        <v>824361</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>499112</v>
+        <v>499919</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1383083</v>
+        <v>1375285</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>597618</v>
+        <v>601388</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1656623</v>
+        <v>1652956</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2486335</v>
+        <v>2510950</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>6889326</v>
+        <v>6900440</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49700</v>
+        <v>50284</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>149540</v>
+        <v>150268</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1207169</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>3323598</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>804176</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2217786</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>59891292</v>
+        <v>64012389</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>53366267</v>
+        <v>53129912</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>52160359</v>
+        <v>51934184</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>143346350</v>
+        <v>143890341</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1205908</v>
+        <v>1195728</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>3314408</v>
+        <v>3314581</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1989545</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>5513604</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>636176</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1761290</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>397731</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1099453</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>477902</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1318681</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>359172</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>989321</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>240042</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>660256</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>200524</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>551119</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>894963</v>
+        <v>904143</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2479555</v>
+        <v>2484804</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>695806</v>
+        <v>704044</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1925468</v>
+        <v>1936226</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>596801</v>
+        <v>603560</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1648751</v>
+        <v>1662071</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4483195</v>
+        <v>4522706</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>12362822</v>
+        <v>12475884</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>199704</v>
+        <v>200654</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>597519</v>
+        <v>554507</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>350362</v>
+        <v>350322</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1046955</v>
+        <v>1054110</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401347</v>
+        <v>350322</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1198615</v>
+        <v>1054110</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50255</v>
+        <v>49809</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>150119</v>
+        <v>150108</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>179031</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>539337</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>347901</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>963014</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>119334</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>358499</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>89628</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>268745</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>149702</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>448062</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>500257</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1375798</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80234</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>239630</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60289</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>180070</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100586</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>300677</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70411</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>210783</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50243</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>150681</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40119</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>120546</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30018</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>90340</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27047919</v>
+        <v>25495725</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31596711</v>
+        <v>28829449</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>198895</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>551087</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>80344</v>
+        <v>79567</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>241113</v>
+        <v>238973</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26967575</v>
+        <v>25615053</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2799219</v>
+        <v>2795345</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>8428025</v>
+        <v>8364718</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24168356</v>
+        <v>22819708</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24168356</v>
+        <v>22819708</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24168356</v>
+        <v>22819708</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24168356</v>
+        <v>22819708</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24168356</v>
+        <v>22819708</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
